--- a/output/pdf_financials_xlsx/STRM.xlsx
+++ b/output/pdf_financials_xlsx/STRM.xlsx
@@ -909,22 +909,22 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.006647</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.020778</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005406</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00281</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007106</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1630,22 +1630,22 @@
         <v>-0.301301</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.481166</v>
+        <v>-3.487813</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.523454</v>
+        <v>-1.502676</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-4.78099</v>
+        <v>-4.775584</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.686513</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-4.485453</v>
+        <v>-4.482643</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.67619</v>
+        <v>-3.669084</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-1.23495</v>
@@ -1720,22 +1720,22 @@
         <v>-0.301301</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.481166</v>
+        <v>-3.487813</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.523454</v>
+        <v>-1.502676</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-4.78099</v>
+        <v>-4.775584</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.686513</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-4.485453</v>
+        <v>-4.482643</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.67619</v>
+        <v>-3.669084</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-1.23495</v>
@@ -1942,37 +1942,37 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000568</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001948</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.20624</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>4.394892</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.172346</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.081902</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.14605</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.309295</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.255784</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.028158</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.091151</v>
       </c>
     </row>
     <row r="35">
@@ -2032,37 +2032,37 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000568</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001948</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.20624</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>4.394892</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.172346</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.081902</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.14605</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.309295</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.255784</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.028158</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.091151</v>
       </c>
     </row>
     <row r="37">
@@ -2578,31 +2578,31 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.198672</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>4.658201</v>
+        <v>0.263309</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.22377</v>
+        <v>0.051424</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.136604</v>
+        <v>0.054702</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.154598</v>
+        <v>0.008548</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.675206</v>
+        <v>0.365911</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.454496</v>
+        <v>0.198712</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.039072</v>
+        <v>0.010914</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.094457</v>
+        <v>0.003306</v>
       </c>
     </row>
     <row r="49">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -16130,7 +16130,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">

--- a/output/pdf_financials_xlsx/STRM.xlsx
+++ b/output/pdf_financials_xlsx/STRM.xlsx
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.275279</v>
+        <v>0.320279</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.111951</v>
+        <v>0.126951</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.204581</v>
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.275279</v>
+        <v>0.320279</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.111951</v>
+        <v>0.126951</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0.204581</v>
@@ -3322,13 +3322,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.001759</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.02062</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.156767</v>
       </c>
       <c r="F64" s="3" t="n">
         <v>0</v>
@@ -3457,13 +3457,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0146</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.0101</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>0</v>
@@ -14214,7 +14214,11 @@
           <t>Share issued for cash</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -14444,7 +14448,11 @@
           <t>Private placement 925,000 185,000</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -17574,7 +17582,11 @@
           <t>Directors fees (Note 6)</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -18492,7 +18504,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
